--- a/output/hmb/ALP-HMB-SUM-NG-100.xlsx
+++ b/output/hmb/ALP-HMB-SUM-NG-100.xlsx
@@ -460,7 +460,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>engine hmb v1.1.0 | data a363d729afc29597 | 2026-09-28T03:15:47Z</t>
+          <t>engine hmb v1.1.1 | data a753f3df87285dba | 2026-09-28T14:33:04Z</t>
         </is>
       </c>
     </row>
@@ -1970,7 +1970,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>engine hmb v1.1.0 | data a363d729afc29597 | 2026-09-28T03:15:47Z</t>
+          <t>engine hmb v1.1.1 | data a753f3df87285dba | 2026-09-28T14:33:04Z</t>
         </is>
       </c>
     </row>
@@ -2521,7 +2521,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>engine hmb v1.1.0 | data a363d729afc29597 | 2026-09-28T03:15:47Z</t>
+          <t>engine hmb v1.1.1 | data a753f3df87285dba | 2026-09-28T14:33:04Z</t>
         </is>
       </c>
     </row>
@@ -3591,7 +3591,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>engine hmb v1.1.0 | data a363d729afc29597 | 2026-09-28T03:15:47Z</t>
+          <t>engine hmb v1.1.1 | data a753f3df87285dba | 2026-09-28T14:33:04Z</t>
         </is>
       </c>
     </row>
@@ -4000,7 +4000,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>engine hmb v1.1.0 | data a363d729afc29597 | 2026-09-28T03:15:47Z</t>
+          <t>engine hmb v1.1.1 | data a753f3df87285dba | 2026-09-28T14:33:04Z</t>
         </is>
       </c>
     </row>

--- a/output/hmb/ALP-HMB-SUM-NG-100.xlsx
+++ b/output/hmb/ALP-HMB-SUM-NG-100.xlsx
@@ -460,7 +460,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>engine hmb v1.1.1 | data a753f3df87285dba | 2026-09-28T14:33:04Z</t>
+          <t>engine hmb v1.1.1 | data 9f2d118f58330dd9 | 2026-09-28T19:00:37Z</t>
         </is>
       </c>
     </row>
@@ -1970,7 +1970,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>engine hmb v1.1.1 | data a753f3df87285dba | 2026-09-28T14:33:04Z</t>
+          <t>engine hmb v1.1.1 | data 9f2d118f58330dd9 | 2026-09-28T19:00:37Z</t>
         </is>
       </c>
     </row>
@@ -2521,7 +2521,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>engine hmb v1.1.1 | data a753f3df87285dba | 2026-09-28T14:33:04Z</t>
+          <t>engine hmb v1.1.1 | data 9f2d118f58330dd9 | 2026-09-28T19:00:37Z</t>
         </is>
       </c>
     </row>
@@ -3591,7 +3591,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>engine hmb v1.1.1 | data a753f3df87285dba | 2026-09-28T14:33:04Z</t>
+          <t>engine hmb v1.1.1 | data 9f2d118f58330dd9 | 2026-09-28T19:00:37Z</t>
         </is>
       </c>
     </row>
@@ -4000,7 +4000,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>engine hmb v1.1.1 | data a753f3df87285dba | 2026-09-28T14:33:04Z</t>
+          <t>engine hmb v1.1.1 | data 9f2d118f58330dd9 | 2026-09-28T19:00:37Z</t>
         </is>
       </c>
     </row>

--- a/output/hmb/ALP-HMB-SUM-NG-100.xlsx
+++ b/output/hmb/ALP-HMB-SUM-NG-100.xlsx
@@ -460,7 +460,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>engine hmb v1.1.1 | data 9f2d118f58330dd9 | 2026-09-28T19:00:37Z</t>
+          <t>engine hmb v1.1.1 | data a6baea26d6584942 | 2026-09-29T02:54:45Z</t>
         </is>
       </c>
     </row>
@@ -1970,7 +1970,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>engine hmb v1.1.1 | data 9f2d118f58330dd9 | 2026-09-28T19:00:37Z</t>
+          <t>engine hmb v1.1.1 | data a6baea26d6584942 | 2026-09-29T02:54:45Z</t>
         </is>
       </c>
     </row>
@@ -2521,7 +2521,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>engine hmb v1.1.1 | data 9f2d118f58330dd9 | 2026-09-28T19:00:37Z</t>
+          <t>engine hmb v1.1.1 | data a6baea26d6584942 | 2026-09-29T02:54:45Z</t>
         </is>
       </c>
     </row>
@@ -3134,7 +3134,7 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>320</v>
+        <v>160</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -3179,7 +3179,7 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>260</v>
+        <v>180</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -3224,7 +3224,7 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>450</v>
+        <v>250</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -3591,7 +3591,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>engine hmb v1.1.1 | data 9f2d118f58330dd9 | 2026-09-28T19:00:37Z</t>
+          <t>engine hmb v1.1.1 | data a6baea26d6584942 | 2026-09-29T02:54:45Z</t>
         </is>
       </c>
     </row>
@@ -3664,7 +3664,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>9.914678150937139</v>
+        <v>9.474678150937139</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -3694,7 +3694,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>545.7663218490628</v>
+        <v>546.2063218490628</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -3739,7 +3739,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>5806.830692544419</v>
+        <v>5802.152962898102</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -3754,7 +3754,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>61.99595253607374</v>
+        <v>62.04593403552474</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -3769,7 +3769,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2.074307928906574</v>
+        <v>1.995359663346139</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -4000,7 +4000,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>engine hmb v1.1.1 | data 9f2d118f58330dd9 | 2026-09-28T19:00:37Z</t>
+          <t>engine hmb v1.1.1 | data a6baea26d6584942 | 2026-09-29T02:54:45Z</t>
         </is>
       </c>
     </row>
@@ -4108,7 +4108,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>gas flow 91,121 Sm3/h = 79.2 % of DP-OWNR-0033 (115,000 Sm3/h)</t>
+          <t>gas flow 91,121 Sm3/h = 75.9 % of DP-OWNR-0033 (120,000 Sm3/h)</t>
         </is>
       </c>
     </row>

--- a/output/hmb/ALP-HMB-SUM-NG-100.xlsx
+++ b/output/hmb/ALP-HMB-SUM-NG-100.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M31"/>
+  <dimension ref="A1:M32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -460,7 +460,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>engine hmb v1.1.1 | data a6baea26d6584942 | 2026-09-29T02:54:45Z</t>
+          <t>engine hmb v1.1.1 | data b6f4b950c7f3b7e0 | 2026-09-29T03:02:22Z</t>
         </is>
       </c>
     </row>
@@ -1931,6 +1931,56 @@
       <c r="M31" t="inlineStr">
         <is>
           <t>source:SRC-IECE-0005</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>31</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Fuel gas to the station preheater burners (water-bath heaters)</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>fuel_gas</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>FGS</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>PHB</t>
+        </is>
+      </c>
+      <c r="F32" t="n">
+        <v>0.0176</v>
+      </c>
+      <c r="G32" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="H32" t="n">
+        <v>25</v>
+      </c>
+      <c r="J32" t="n">
+        <v>0</v>
+      </c>
+      <c r="K32" t="n">
+        <v>0</v>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>preliminary</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>decision:DEC-EPCE-0014</t>
         </is>
       </c>
     </row>
@@ -1945,7 +1995,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J17"/>
+  <dimension ref="A1:J18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -1970,7 +2020,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>engine hmb v1.1.1 | data a6baea26d6584942 | 2026-09-29T02:54:45Z</t>
+          <t>engine hmb v1.1.1 | data b6f4b950c7f3b7e0 | 2026-09-29T03:02:22Z</t>
         </is>
       </c>
     </row>
@@ -2231,7 +2281,7 @@
         <v>0</v>
       </c>
       <c r="D10" t="n">
-        <v>18.541</v>
+        <v>18.559</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
@@ -2357,29 +2407,29 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>PIPE</t>
+          <t>PHB</t>
         </is>
       </c>
       <c r="B14" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C14" t="n">
-        <v>310.46</v>
+        <v>0.018</v>
       </c>
       <c r="D14" t="n">
-        <v>310.46</v>
+        <v>0</v>
       </c>
       <c r="E14" t="n">
-        <v>1072.285</v>
+        <v>0</v>
       </c>
       <c r="F14" t="n">
-        <v>1071.964</v>
+        <v>0</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>0.321</v>
+        <v>0</v>
       </c>
       <c r="I14" t="n">
         <v>0</v>
@@ -2389,29 +2439,29 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>SEA</t>
+          <t>PIPE</t>
         </is>
       </c>
       <c r="B15" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>0</v>
+        <v>310.46</v>
       </c>
       <c r="D15" t="n">
-        <v>10196.804</v>
+        <v>310.46</v>
       </c>
       <c r="E15" t="n">
-        <v>0</v>
+        <v>1072.285</v>
       </c>
       <c r="F15" t="n">
-        <v>995.877</v>
+        <v>1071.964</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>-995.877</v>
+        <v>0.321</v>
       </c>
       <c r="I15" t="n">
         <v>0</v>
@@ -2421,70 +2471,102 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>ST</t>
+          <t>SEA</t>
         </is>
       </c>
       <c r="B16" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C16" t="n">
-        <v>216.05</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>216.051</v>
+        <v>10196.804</v>
       </c>
       <c r="E16" t="n">
-        <v>775.587</v>
+        <v>0</v>
       </c>
       <c r="F16" t="n">
-        <v>587.971</v>
+        <v>995.877</v>
       </c>
       <c r="G16" t="n">
-        <v>187.619</v>
+        <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.002</v>
+        <v>-995.877</v>
       </c>
       <c r="I16" t="n">
         <v>0</v>
       </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>ST: shaft power (output / mechanical / generator efficiency)</t>
-        </is>
-      </c>
+      <c r="J16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
+          <t>ST</t>
+        </is>
+      </c>
+      <c r="B17" t="b">
+        <v>0</v>
+      </c>
+      <c r="C17" t="n">
+        <v>216.05</v>
+      </c>
+      <c r="D17" t="n">
+        <v>216.051</v>
+      </c>
+      <c r="E17" t="n">
+        <v>775.587</v>
+      </c>
+      <c r="F17" t="n">
+        <v>587.971</v>
+      </c>
+      <c r="G17" t="n">
+        <v>187.619</v>
+      </c>
+      <c r="H17" t="n">
+        <v>-0.002</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>ST: shaft power (output / mechanical / generator efficiency)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
           <t>STK</t>
         </is>
       </c>
-      <c r="B17" t="b">
+      <c r="B18" t="b">
         <v>1</v>
       </c>
-      <c r="C17" t="n">
+      <c r="C18" t="n">
         <v>729.521</v>
       </c>
-      <c r="D17" t="n">
-        <v>0</v>
-      </c>
-      <c r="E17" t="n">
+      <c r="D18" t="n">
+        <v>0</v>
+      </c>
+      <c r="E18" t="n">
         <v>43.976</v>
       </c>
-      <c r="F17" t="n">
-        <v>0</v>
-      </c>
-      <c r="G17" t="n">
-        <v>0</v>
-      </c>
-      <c r="H17" t="n">
+      <c r="F18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G18" t="n">
+        <v>0</v>
+      </c>
+      <c r="H18" t="n">
         <v>43.976</v>
       </c>
-      <c r="I17" t="n">
-        <v>0</v>
-      </c>
-      <c r="J17" t="inlineStr"/>
+      <c r="I18" t="n">
+        <v>0</v>
+      </c>
+      <c r="J18" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2521,7 +2603,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>engine hmb v1.1.1 | data a6baea26d6584942 | 2026-09-29T02:54:45Z</t>
+          <t>engine hmb v1.1.1 | data b6f4b950c7f3b7e0 | 2026-09-29T03:02:22Z</t>
         </is>
       </c>
     </row>
@@ -3591,7 +3673,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>engine hmb v1.1.1 | data a6baea26d6584942 | 2026-09-29T02:54:45Z</t>
+          <t>engine hmb v1.1.1 | data b6f4b950c7f3b7e0 | 2026-09-29T03:02:22Z</t>
         </is>
       </c>
     </row>
@@ -3709,7 +3791,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>880.3257301861704</v>
+        <v>881.1613772845619</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -3739,7 +3821,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>5802.152962898102</v>
+        <v>5807.660642750699</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -3754,7 +3836,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>62.04593403552474</v>
+        <v>61.98709293549428</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -3814,7 +3896,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>18.541</v>
+        <v>18.5586</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -3829,7 +3911,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>91121.32184016959</v>
+        <v>91207.81853745597</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -4000,7 +4082,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>engine hmb v1.1.1 | data a6baea26d6584942 | 2026-09-29T02:54:45Z</t>
+          <t>engine hmb v1.1.1 | data b6f4b950c7f3b7e0 | 2026-09-29T03:02:22Z</t>
         </is>
       </c>
     </row>
@@ -4108,7 +4190,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>gas flow 91,121 Sm3/h = 75.9 % of DP-OWNR-0033 (120,000 Sm3/h)</t>
+          <t>gas flow 91,208 Sm3/h = 76.0 % of DP-OWNR-0033 (120,000 Sm3/h)</t>
         </is>
       </c>
     </row>

--- a/output/hmb/ALP-HMB-SUM-NG-100.xlsx
+++ b/output/hmb/ALP-HMB-SUM-NG-100.xlsx
@@ -460,7 +460,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>engine hmb v1.1.1 | data b6f4b950c7f3b7e0 | 2026-09-29T03:02:22Z</t>
+          <t>engine hmb v1.2.0 | data 015d1cd1c6fdda54 | 2026-09-29T03:07:46Z</t>
         </is>
       </c>
     </row>
@@ -2020,7 +2020,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>engine hmb v1.1.1 | data b6f4b950c7f3b7e0 | 2026-09-29T03:02:22Z</t>
+          <t>engine hmb v1.2.0 | data 015d1cd1c6fdda54 | 2026-09-29T03:07:46Z</t>
         </is>
       </c>
     </row>
@@ -2603,7 +2603,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>engine hmb v1.1.1 | data b6f4b950c7f3b7e0 | 2026-09-29T03:02:22Z</t>
+          <t>engine hmb v1.2.0 | data 015d1cd1c6fdda54 | 2026-09-29T03:07:46Z</t>
         </is>
       </c>
     </row>
@@ -3673,7 +3673,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>engine hmb v1.1.1 | data b6f4b950c7f3b7e0 | 2026-09-29T03:02:22Z</t>
+          <t>engine hmb v1.2.0 | data 015d1cd1c6fdda54 | 2026-09-29T03:07:46Z</t>
         </is>
       </c>
     </row>
@@ -4082,7 +4082,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>engine hmb v1.1.1 | data b6f4b950c7f3b7e0 | 2026-09-29T03:02:22Z</t>
+          <t>engine hmb v1.2.0 | data 015d1cd1c6fdda54 | 2026-09-29T03:07:46Z</t>
         </is>
       </c>
     </row>

--- a/output/hmb/ALP-HMB-SUM-NG-100.xlsx
+++ b/output/hmb/ALP-HMB-SUM-NG-100.xlsx
@@ -460,7 +460,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>engine hmb v1.2.0 | data 015d1cd1c6fdda54 | 2026-09-29T03:07:46Z</t>
+          <t>engine hmb v1.2.0 | data 6b60fce553593bf5 | 2026-09-29T03:49:51Z</t>
         </is>
       </c>
     </row>
@@ -2020,7 +2020,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>engine hmb v1.2.0 | data 015d1cd1c6fdda54 | 2026-09-29T03:07:46Z</t>
+          <t>engine hmb v1.2.0 | data 6b60fce553593bf5 | 2026-09-29T03:49:51Z</t>
         </is>
       </c>
     </row>
@@ -2603,7 +2603,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>engine hmb v1.2.0 | data 015d1cd1c6fdda54 | 2026-09-29T03:07:46Z</t>
+          <t>engine hmb v1.2.0 | data 6b60fce553593bf5 | 2026-09-29T03:49:51Z</t>
         </is>
       </c>
     </row>
@@ -3673,7 +3673,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>engine hmb v1.2.0 | data 015d1cd1c6fdda54 | 2026-09-29T03:07:46Z</t>
+          <t>engine hmb v1.2.0 | data 6b60fce553593bf5 | 2026-09-29T03:49:51Z</t>
         </is>
       </c>
     </row>
@@ -4065,7 +4065,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B11"/>
+  <dimension ref="A1:B12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -4082,7 +4082,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>engine hmb v1.2.0 | data 015d1cd1c6fdda54 | 2026-09-29T03:07:46Z</t>
+          <t>engine hmb v1.2.0 | data 6b60fce553593bf5 | 2026-09-29T03:49:51Z</t>
         </is>
       </c>
     </row>
@@ -4189,6 +4189,18 @@
         </is>
       </c>
       <c r="B11" t="inlineStr">
+        <is>
+          <t>CW temperature rise 6.61 K vs DP-CASE-0015 &lt;= 7.0 K (Condenser cooling water temperature rise)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
         <is>
           <t>gas flow 91,208 Sm3/h = 76.0 % of DP-OWNR-0033 (120,000 Sm3/h)</t>
         </is>
